--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N10_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.05009432606652</v>
+        <v>1.767579473784164</v>
       </c>
       <c r="D2" t="n">
-        <v>10.47090827867309</v>
+        <v>2.273182682965432</v>
       </c>
       <c r="E2" t="n">
-        <v>5.178601545130427</v>
+        <v>5.502827552309858</v>
       </c>
       <c r="F2" t="n">
-        <v>5.532853059053125</v>
+        <v>5.946929571809517</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>6.629535411539548</v>
+        <v>11.05009432606652</v>
       </c>
       <c r="D3" t="n">
-        <v>7.081461677654484</v>
+        <v>10.47090827867309</v>
       </c>
       <c r="E3" t="n">
-        <v>5.178601545130427</v>
+        <v>5.502827552309858</v>
       </c>
       <c r="F3" t="n">
-        <v>5.532853059053125</v>
+        <v>5.946929571809517</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.41068226286025</v>
+        <v>6.629535411539548</v>
       </c>
       <c r="D4" t="n">
-        <v>16.55473663006916</v>
+        <v>7.081461677654484</v>
       </c>
       <c r="E4" t="n">
-        <v>5.178601545130427</v>
+        <v>5.502827552309858</v>
       </c>
       <c r="F4" t="n">
-        <v>5.532853059053125</v>
+        <v>5.946929571809517</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.757130878006782</v>
+        <v>15.41068226286025</v>
       </c>
       <c r="D5" t="n">
-        <v>7.163622713427754</v>
+        <v>16.55473663006916</v>
       </c>
       <c r="E5" t="n">
-        <v>5.178601545130427</v>
+        <v>5.502827552309858</v>
       </c>
       <c r="F5" t="n">
-        <v>5.532853059053125</v>
+        <v>5.946929571809517</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.966304553723561</v>
+        <v>5.757130878006782</v>
       </c>
       <c r="D6" t="n">
-        <v>2.946268637397485</v>
+        <v>7.163622713427754</v>
       </c>
       <c r="E6" t="n">
-        <v>5.178601545130427</v>
+        <v>5.502827552309858</v>
       </c>
       <c r="F6" t="n">
-        <v>5.532853059053125</v>
+        <v>5.946929571809517</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.5325981049723</v>
+        <v>3.966304553723561</v>
       </c>
       <c r="D7" t="n">
-        <v>21.70378871175363</v>
+        <v>2.946268637397485</v>
       </c>
       <c r="E7" t="n">
-        <v>5.178601545130427</v>
+        <v>5.502827552309858</v>
       </c>
       <c r="F7" t="n">
-        <v>5.532853059053125</v>
+        <v>5.946929571809517</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.705470781521938</v>
+        <v>20.5325981049723</v>
       </c>
       <c r="D8" t="n">
-        <v>16.10249559363569</v>
+        <v>21.70378871175363</v>
       </c>
       <c r="E8" t="n">
-        <v>5.178601545130427</v>
+        <v>5.502827552309858</v>
       </c>
       <c r="F8" t="n">
-        <v>5.532853059053125</v>
+        <v>5.946929571809517</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.736325114649519</v>
+        <v>4.705470781521938</v>
       </c>
       <c r="D9" t="n">
-        <v>8.706763793456958</v>
+        <v>16.10249559363569</v>
       </c>
       <c r="E9" t="n">
-        <v>5.178601545130427</v>
+        <v>5.502827552309858</v>
       </c>
       <c r="F9" t="n">
-        <v>5.532853059053125</v>
+        <v>5.946929571809517</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,23 +736,55 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
+        <v>9.736325114649519</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8.706763793456958</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5.502827552309858</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5.946929571809517</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>W0035F0002T0006Z000C1N10.png</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" t="n">
         <v>12.48733580263848</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>13.59324614939033</v>
       </c>
-      <c r="E10" t="n">
-        <v>5.178601545130427</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5.532853059053125</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>T6165</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="E11" t="n">
+        <v>5.502827552309858</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.946929571809517</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0002T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.767579473784164</v>
+        <v>0.2872316644899267</v>
       </c>
       <c r="D2" t="n">
-        <v>2.273182682965432</v>
+        <v>0.3693921859818827</v>
       </c>
       <c r="E2" t="n">
-        <v>5.502827552309858</v>
+        <v>0.894209477250352</v>
       </c>
       <c r="F2" t="n">
-        <v>5.946929571809517</v>
+        <v>0.9663760554190466</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.05009432606652</v>
+        <v>1.795640327985809</v>
       </c>
       <c r="D3" t="n">
-        <v>10.47090827867309</v>
+        <v>1.701522595284378</v>
       </c>
       <c r="E3" t="n">
-        <v>5.502827552309858</v>
+        <v>0.894209477250352</v>
       </c>
       <c r="F3" t="n">
-        <v>5.946929571809517</v>
+        <v>0.9663760554190466</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.629535411539548</v>
+        <v>1.077299504375177</v>
       </c>
       <c r="D4" t="n">
-        <v>7.081461677654484</v>
+        <v>1.150737522618854</v>
       </c>
       <c r="E4" t="n">
-        <v>5.502827552309858</v>
+        <v>0.894209477250352</v>
       </c>
       <c r="F4" t="n">
-        <v>5.946929571809517</v>
+        <v>0.9663760554190466</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.41068226286025</v>
+        <v>2.504235867714791</v>
       </c>
       <c r="D5" t="n">
-        <v>16.55473663006916</v>
+        <v>2.690144702386239</v>
       </c>
       <c r="E5" t="n">
-        <v>5.502827552309858</v>
+        <v>0.894209477250352</v>
       </c>
       <c r="F5" t="n">
-        <v>5.946929571809517</v>
+        <v>0.9663760554190466</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.757130878006782</v>
+        <v>0.9355337676761021</v>
       </c>
       <c r="D6" t="n">
-        <v>7.163622713427754</v>
+        <v>1.16408869093201</v>
       </c>
       <c r="E6" t="n">
-        <v>5.502827552309858</v>
+        <v>0.894209477250352</v>
       </c>
       <c r="F6" t="n">
-        <v>5.946929571809517</v>
+        <v>0.9663760554190466</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.966304553723561</v>
+        <v>0.6445244899800787</v>
       </c>
       <c r="D7" t="n">
-        <v>2.946268637397485</v>
+        <v>0.4787686535770913</v>
       </c>
       <c r="E7" t="n">
-        <v>5.502827552309858</v>
+        <v>0.894209477250352</v>
       </c>
       <c r="F7" t="n">
-        <v>5.946929571809517</v>
+        <v>0.9663760554190466</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.5325981049723</v>
+        <v>3.336547192058</v>
       </c>
       <c r="D8" t="n">
-        <v>21.70378871175363</v>
+        <v>3.526865665659966</v>
       </c>
       <c r="E8" t="n">
-        <v>5.502827552309858</v>
+        <v>0.894209477250352</v>
       </c>
       <c r="F8" t="n">
-        <v>5.946929571809517</v>
+        <v>0.9663760554190466</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>4.705470781521938</v>
+        <v>0.7646390019973149</v>
       </c>
       <c r="D9" t="n">
-        <v>16.10249559363569</v>
+        <v>2.616655533965799</v>
       </c>
       <c r="E9" t="n">
-        <v>5.502827552309858</v>
+        <v>0.894209477250352</v>
       </c>
       <c r="F9" t="n">
-        <v>5.946929571809517</v>
+        <v>0.9663760554190466</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.736325114649519</v>
+        <v>1.582152831130547</v>
       </c>
       <c r="D10" t="n">
-        <v>8.706763793456958</v>
+        <v>1.414849116436756</v>
       </c>
       <c r="E10" t="n">
-        <v>5.502827552309858</v>
+        <v>0.894209477250352</v>
       </c>
       <c r="F10" t="n">
-        <v>5.946929571809517</v>
+        <v>0.9663760554190466</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>12.48733580263848</v>
+        <v>2.029192067928753</v>
       </c>
       <c r="D11" t="n">
-        <v>13.59324614939033</v>
+        <v>2.208902499275928</v>
       </c>
       <c r="E11" t="n">
-        <v>5.502827552309858</v>
+        <v>0.894209477250352</v>
       </c>
       <c r="F11" t="n">
-        <v>5.946929571809517</v>
+        <v>0.9663760554190466</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
